--- a/haklaut/menu.xlsx
+++ b/haklaut/menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC8CA3EB-4422-4430-803D-47A74A208D45}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0E1CDE4-6874-40A3-B9BA-3E7852F8B2B2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,105 +57,39 @@
     <t>מערכת החיסון</t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/mavo.html</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/visut-hom-klali.html</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/visut-hom-haklai.html</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/maarehet-hisun.html</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/maarehet-neshima.html</t>
-  </si>
-  <si>
     <t>מערכת הנשימה</t>
   </si>
   <si>
     <t>מערכת הרבייה</t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/maarehet-revaya.html</t>
-  </si>
-  <si>
     <t>menu_icon</t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/mavo.png</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/visut.png</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/visut-haklai.png</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/hisun.png</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/neshima.png</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/revaya.png</t>
-  </si>
-  <si>
     <t>general</t>
   </si>
   <si>
     <t>dogs</t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/klavim/tkufot-kritiyot.html</t>
-  </si>
-  <si>
     <t xml:space="preserve">תקופות קריטיות </t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/tkufot.png</t>
-  </si>
-  <si>
     <t>topic</t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/ikul.png</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/ikul.html</t>
-  </si>
-  <si>
     <t>מערכת העיכול</t>
   </si>
   <si>
     <t>רבייה</t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/klavim/reviya.html</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/dog-reviya.png</t>
-  </si>
-  <si>
     <t xml:space="preserve">הזנה וטיפוח </t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/klavim/hazana-parva.html</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/mazon.png</t>
-  </si>
-  <si>
     <t>כלבת</t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/kalevet.png</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/klavim/kalevet.html</t>
-  </si>
-  <si>
     <t>sub_title</t>
   </si>
   <si>
@@ -195,25 +129,91 @@
     <t>יצרים</t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/klavim/yezarim.html</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/yezarim.png</t>
-  </si>
-  <si>
     <t>מה מניע את הכלב: יצרים, דחפים, תכונות, מזג ותחומי הדיגר</t>
   </si>
   <si>
     <t>כיצד כלבים לומדים</t>
   </si>
   <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/klavim/lemida.html</t>
-  </si>
-  <si>
-    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/lemida.png</t>
-  </si>
-  <si>
     <t>תקופות קריטיות, אינסטינקט, רפלקס, התניה קלאסית ואופרנטית, חיזוקים ועונש</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/mavo.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/mavo.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/visut-hom-klali.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/visut.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/visut-hom-haklai.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/visut-haklai.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/maarehet-hisun.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/hisun.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/maarehet-neshima.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/neshima.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/ikul.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/ikul.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/maarehet-revaya.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/revaya.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/klavim/tkufot-kritiyot.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/klavin/tkufot.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/klavim/reviya.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/klavin/dog-reviya.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/klavim/hazana-parva.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/klavin/mazon.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/klavim/kalevet.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/klavin/kalevet.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/klavim/yezarim.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/klavin/yezarim.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/klavim/lemida.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/bg/klavin/lemida.png</t>
   </si>
 </sst>
 </file>
@@ -595,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -609,16 +609,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -626,16 +626,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -643,16 +643,16 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -660,195 +660,195 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{3F08E3EC-5CAE-4D20-8ED6-CA53A0399477}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{5B7C2E5E-FF93-4D57-9D21-5E1CE71A6E26}"/>
-    <hyperlink ref="C3" r:id="rId3" xr:uid="{9F886686-24BD-404C-8510-11CE4016BC5E}"/>
-    <hyperlink ref="C4" r:id="rId4" xr:uid="{A5633CDD-BA5F-4464-9AF3-41D9D333F7A0}"/>
-    <hyperlink ref="C5" r:id="rId5" xr:uid="{0420DAF3-5C87-4EF0-86B0-C9EC73041236}"/>
-    <hyperlink ref="C6" r:id="rId6" xr:uid="{1E8E77D7-0763-44D9-A2C1-CE019D205ABE}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{65A3D81C-4BDC-47AA-B7B8-A5836CDE36EF}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{B9CC987C-C4B1-4390-B0CD-E686D05DFA3D}"/>
-    <hyperlink ref="C7" r:id="rId9" xr:uid="{2402C49A-7D42-44AD-9335-3BB0432A3A1A}"/>
-    <hyperlink ref="B6" r:id="rId10" xr:uid="{7517147F-D231-45F6-8908-95B66EE43EAC}"/>
-    <hyperlink ref="B7" r:id="rId11" xr:uid="{119C3298-48AF-47F3-B5F4-812F2FBD31A4}"/>
-    <hyperlink ref="B9" r:id="rId12" xr:uid="{513D8D30-3F75-490B-B291-D14B90226E33}"/>
-    <hyperlink ref="B10" r:id="rId13" xr:uid="{85602228-8211-454E-9E45-26DB0D927C0F}"/>
-    <hyperlink ref="C10" r:id="rId14" xr:uid="{BF36189E-474B-48FC-986F-A4627A52C309}"/>
-    <hyperlink ref="C11" r:id="rId15" xr:uid="{18DB512F-3622-485E-AB55-7A1A43B47F6B}"/>
-    <hyperlink ref="B11" r:id="rId16" xr:uid="{7F9343F3-483B-47E3-BCE6-087AB06A5E42}"/>
-    <hyperlink ref="C12" r:id="rId17" xr:uid="{EEA251E9-BB9D-4ED2-8884-85CF4894F9B4}"/>
-    <hyperlink ref="B12" r:id="rId18" xr:uid="{D54F77F3-7EBA-4EDB-BA20-9F72E40554AC}"/>
-    <hyperlink ref="C13" r:id="rId19" xr:uid="{D40292C3-27B3-4AA1-8410-555541F03DD4}"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://tanyatabakmaher.github.io/haklaut/mavo.html" xr:uid="{3F08E3EC-5CAE-4D20-8ED6-CA53A0399477}"/>
+    <hyperlink ref="C2" r:id="rId2" display="https://tanyatabakmaher.github.io/haklaut/bg/mavo.png" xr:uid="{5B7C2E5E-FF93-4D57-9D21-5E1CE71A6E26}"/>
+    <hyperlink ref="C3" r:id="rId3" display="https://tanyatabakmaher.github.io/haklaut/bg/visut.png" xr:uid="{9F886686-24BD-404C-8510-11CE4016BC5E}"/>
+    <hyperlink ref="C4" r:id="rId4" display="https://tanyatabakmaher.github.io/haklaut/bg/visut-haklai.png" xr:uid="{A5633CDD-BA5F-4464-9AF3-41D9D333F7A0}"/>
+    <hyperlink ref="C5" r:id="rId5" display="https://tanyatabakmaher.github.io/haklaut/bg/hisun.png" xr:uid="{0420DAF3-5C87-4EF0-86B0-C9EC73041236}"/>
+    <hyperlink ref="C6" r:id="rId6" display="https://bagruyot.org/haklaut//bg/neshima.png" xr:uid="{1E8E77D7-0763-44D9-A2C1-CE019D205ABE}"/>
+    <hyperlink ref="C8" r:id="rId7" display="https://tanyatabakmaher.github.io/haklaut/bg/revaya.png" xr:uid="{65A3D81C-4BDC-47AA-B7B8-A5836CDE36EF}"/>
+    <hyperlink ref="C9" r:id="rId8" display="https://tanyatabakmaher.github.io/haklaut/bg/klavin/tkufot.png" xr:uid="{B9CC987C-C4B1-4390-B0CD-E686D05DFA3D}"/>
+    <hyperlink ref="C7" r:id="rId9" display="https://tanyatabakmaher.github.io/haklaut/bg/ikul.png" xr:uid="{2402C49A-7D42-44AD-9335-3BB0432A3A1A}"/>
+    <hyperlink ref="B6" r:id="rId10" display="https://tanyatabakmaher.github.io/haklaut/maarehet-neshima.html" xr:uid="{7517147F-D231-45F6-8908-95B66EE43EAC}"/>
+    <hyperlink ref="B7" r:id="rId11" display="https://tanyatabakmaher.github.io/haklaut/ikul.html" xr:uid="{119C3298-48AF-47F3-B5F4-812F2FBD31A4}"/>
+    <hyperlink ref="B9" r:id="rId12" display="https://tanyatabakmaher.github.io/haklaut/klavim/tkufot-kritiyot.html" xr:uid="{513D8D30-3F75-490B-B291-D14B90226E33}"/>
+    <hyperlink ref="B10" r:id="rId13" display="https://tanyatabakmaher.github.io/haklaut/klavim/reviya.html" xr:uid="{85602228-8211-454E-9E45-26DB0D927C0F}"/>
+    <hyperlink ref="C10" r:id="rId14" display="https://tanyatabakmaher.github.io/haklaut/bg/klavin/dog-reviya.png" xr:uid="{BF36189E-474B-48FC-986F-A4627A52C309}"/>
+    <hyperlink ref="C11" r:id="rId15" display="https://tanyatabakmaher.github.io/haklaut/bg/klavin/mazon.png" xr:uid="{18DB512F-3622-485E-AB55-7A1A43B47F6B}"/>
+    <hyperlink ref="B11" r:id="rId16" display="https://tanyatabakmaher.github.io/haklaut/klavim/hazana-parva.html" xr:uid="{7F9343F3-483B-47E3-BCE6-087AB06A5E42}"/>
+    <hyperlink ref="C12" r:id="rId17" display="https://tanyatabakmaher.github.io/haklaut/bg/klavin/kalevet.png" xr:uid="{EEA251E9-BB9D-4ED2-8884-85CF4894F9B4}"/>
+    <hyperlink ref="B12" r:id="rId18" display="https://tanyatabakmaher.github.io/haklaut/klavim/kalevet.html" xr:uid="{D54F77F3-7EBA-4EDB-BA20-9F72E40554AC}"/>
+    <hyperlink ref="C13" r:id="rId19" display="https://tanyatabakmaher.github.io/haklaut/bg/klavin/yezarim.png" xr:uid="{D40292C3-27B3-4AA1-8410-555541F03DD4}"/>
     <hyperlink ref="B13" r:id="rId20" xr:uid="{B50778ED-3CC4-43A6-8CC9-F9610CED6D3A}"/>
-    <hyperlink ref="C14" r:id="rId21" xr:uid="{911EC805-60C2-4E6A-8C4A-33407EAE8CF4}"/>
-    <hyperlink ref="B14" r:id="rId22" xr:uid="{EBC0AA92-E021-497F-B4EA-CF4C1550338B}"/>
+    <hyperlink ref="C14" r:id="rId21" display="https://tanyatabakmaher.github.io/haklaut/bg/klavin/lemida.png" xr:uid="{911EC805-60C2-4E6A-8C4A-33407EAE8CF4}"/>
+    <hyperlink ref="B14" r:id="rId22" display="https://tanyatabakmaher.github.io/haklaut/klavim/lemida.html" xr:uid="{EBC0AA92-E021-497F-B4EA-CF4C1550338B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
